--- a/GAP.xlsx
+++ b/GAP.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\1.Finance\Anaylsen\Models\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9048D178-8492-4628-BC15-80510E4E632A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{640509FB-E385-495D-8048-D4BFED727DD8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="19095" yWindow="0" windowWidth="19410" windowHeight="20925" xr2:uid="{45B8ACDC-CB3B-40F4-A3D2-AA5D93D3C1D7}"/>
+    <workbookView xWindow="19095" yWindow="0" windowWidth="19410" windowHeight="20925" activeTab="1" xr2:uid="{45B8ACDC-CB3B-40F4-A3D2-AA5D93D3C1D7}"/>
   </bookViews>
   <sheets>
     <sheet name="Main" sheetId="1" r:id="rId1"/>
@@ -1111,7 +1111,7 @@
         <v>3</v>
       </c>
       <c r="J2" s="2">
-        <v>27.09</v>
+        <v>25.5</v>
       </c>
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.2">
@@ -1137,7 +1137,7 @@
       </c>
       <c r="J4" s="6">
         <f>J3*J2</f>
-        <v>10075.3599366</v>
+        <v>9484.0043700000006</v>
       </c>
       <c r="K4" s="4"/>
     </row>
@@ -1199,7 +1199,7 @@
       </c>
       <c r="J7" s="6">
         <f>J4+J6-J5</f>
-        <v>9049.3599365999999</v>
+        <v>8458.0043700000006</v>
       </c>
     </row>
     <row r="8" spans="1:11" x14ac:dyDescent="0.2">
@@ -1236,7 +1236,7 @@
       </c>
       <c r="J9" s="18">
         <f>+J4/844</f>
-        <v>11.937630256635071</v>
+        <v>11.236972002369669</v>
       </c>
     </row>
     <row r="10" spans="1:11" x14ac:dyDescent="0.2">
@@ -2305,7 +2305,9 @@
       <c r="V15" s="24">
         <v>15086</v>
       </c>
-      <c r="W15" s="24"/>
+      <c r="W15" s="24">
+        <v>15366</v>
+      </c>
       <c r="X15" s="24"/>
       <c r="Y15" s="24"/>
       <c r="Z15" s="24"/>
@@ -2376,7 +2378,9 @@
       <c r="V16" s="6">
         <v>8859</v>
       </c>
-      <c r="W16" s="6"/>
+      <c r="W16" s="6">
+        <v>9098</v>
+      </c>
       <c r="X16" s="6"/>
       <c r="Y16" s="6"/>
       <c r="Z16" s="6"/>
@@ -2456,14 +2460,17 @@
         <v>5359</v>
       </c>
       <c r="U17" s="6">
-        <f t="shared" ref="U17:V17" si="18">U15-U16</f>
+        <f t="shared" ref="U17:W17" si="18">U15-U16</f>
         <v>5775</v>
       </c>
       <c r="V17" s="6">
         <f t="shared" si="18"/>
         <v>6227</v>
       </c>
-      <c r="W17" s="6"/>
+      <c r="W17" s="6">
+        <f t="shared" si="18"/>
+        <v>6268</v>
+      </c>
       <c r="X17" s="6"/>
       <c r="Y17" s="6"/>
       <c r="Z17" s="6"/>
@@ -2534,7 +2541,9 @@
       <c r="V18" s="6">
         <v>5115</v>
       </c>
-      <c r="W18" s="6"/>
+      <c r="W18" s="6">
+        <v>5153</v>
+      </c>
       <c r="X18" s="6"/>
       <c r="Y18" s="6"/>
       <c r="Z18" s="6"/>
@@ -2614,14 +2623,17 @@
         <v>-69</v>
       </c>
       <c r="U19" s="6">
-        <f t="shared" ref="U19:V19" si="26">U17-U18</f>
+        <f t="shared" ref="U19:W19" si="26">U17-U18</f>
         <v>560</v>
       </c>
       <c r="V19" s="6">
         <f t="shared" si="26"/>
         <v>1112</v>
       </c>
-      <c r="W19" s="6"/>
+      <c r="W19" s="6">
+        <f t="shared" si="26"/>
+        <v>1115</v>
+      </c>
       <c r="X19" s="6"/>
       <c r="Y19" s="6"/>
       <c r="Z19" s="6"/>
@@ -2694,7 +2706,9 @@
       <c r="V20" s="6">
         <v>87</v>
       </c>
-      <c r="W20" s="6"/>
+      <c r="W20" s="6">
+        <v>0</v>
+      </c>
       <c r="X20" s="6"/>
       <c r="Y20" s="6"/>
       <c r="Z20" s="6"/>
@@ -2765,7 +2779,9 @@
       <c r="V21" s="6">
         <v>112</v>
       </c>
-      <c r="W21" s="6"/>
+      <c r="W21" s="6">
+        <v>17</v>
+      </c>
       <c r="X21" s="6"/>
       <c r="Y21" s="6"/>
       <c r="Z21" s="6"/>
@@ -2845,14 +2861,17 @@
         <v>-139</v>
       </c>
       <c r="U22" s="6">
-        <f t="shared" ref="U22:V22" si="35">U19-U20+U21</f>
+        <f t="shared" ref="U22:W22" si="35">U19-U20+U21</f>
         <v>556</v>
       </c>
       <c r="V22" s="6">
         <f t="shared" si="35"/>
         <v>1137</v>
       </c>
-      <c r="W22" s="6"/>
+      <c r="W22" s="6">
+        <f t="shared" si="35"/>
+        <v>1132</v>
+      </c>
       <c r="X22" s="6"/>
       <c r="Y22" s="6"/>
       <c r="Z22" s="6"/>
@@ -2923,7 +2942,9 @@
       <c r="V23" s="6">
         <v>293</v>
       </c>
-      <c r="W23" s="6"/>
+      <c r="W23" s="6">
+        <v>316</v>
+      </c>
       <c r="X23" s="6"/>
       <c r="Y23" s="6"/>
       <c r="Z23" s="6"/>
@@ -3003,14 +3024,17 @@
         <v>-202</v>
       </c>
       <c r="U24" s="6">
-        <f t="shared" ref="U24:V24" si="42">U22-U23</f>
+        <f t="shared" ref="U24:W24" si="42">U22-U23</f>
         <v>502</v>
       </c>
       <c r="V24" s="6">
         <f t="shared" si="42"/>
         <v>844</v>
       </c>
-      <c r="W24" s="6"/>
+      <c r="W24" s="6">
+        <f t="shared" si="42"/>
+        <v>816</v>
+      </c>
       <c r="X24" s="6"/>
       <c r="Y24" s="6"/>
       <c r="Z24" s="6"/>
@@ -3052,56 +3076,60 @@
         <v>0.42245989304812837</v>
       </c>
       <c r="H26" s="25">
-        <f>+H24/H27</f>
+        <f t="shared" ref="H26:M26" si="43">+H24/H27</f>
         <v>0.5478723404255319</v>
       </c>
       <c r="I26" s="25">
-        <f>+I24/I27</f>
+        <f t="shared" si="43"/>
         <v>0.72679045092838201</v>
       </c>
       <c r="J26" s="25">
-        <f>+J24/J27</f>
+        <f t="shared" si="43"/>
         <v>0.54641909814323608</v>
       </c>
       <c r="K26" s="25">
-        <f>+K24/K27</f>
+        <f t="shared" si="43"/>
         <v>0.51604278074866305</v>
       </c>
       <c r="L26" s="25">
-        <f>+L24/L27</f>
+        <f t="shared" si="43"/>
         <v>0.579088471849866</v>
       </c>
       <c r="M26" s="25">
-        <f>+M24/M27</f>
+        <f t="shared" si="43"/>
         <v>0.63440860215053763</v>
       </c>
       <c r="P26" s="25">
-        <f t="shared" ref="P26:V26" si="43">P24/P27</f>
+        <f t="shared" ref="P26:W26" si="44">P24/P27</f>
         <v>2.5850515463917527</v>
       </c>
       <c r="Q26" s="25">
-        <f t="shared" si="43"/>
+        <f t="shared" si="44"/>
         <v>0.9285714285714286</v>
       </c>
       <c r="R26" s="25">
-        <f t="shared" si="43"/>
+        <f t="shared" si="44"/>
         <v>-1.7780748663101604</v>
       </c>
       <c r="S26" s="25">
-        <f t="shared" si="43"/>
+        <f t="shared" si="44"/>
         <v>0.68085106382978722</v>
       </c>
       <c r="T26" s="25">
-        <f t="shared" si="43"/>
+        <f t="shared" si="44"/>
         <v>-0.55040871934604907</v>
       </c>
       <c r="U26" s="25">
-        <f t="shared" si="43"/>
+        <f t="shared" si="44"/>
         <v>1.3567567567567567</v>
       </c>
       <c r="V26" s="25">
-        <f t="shared" si="43"/>
+        <f t="shared" si="44"/>
         <v>2.2446808510638299</v>
+      </c>
+      <c r="W26" s="25" t="e">
+        <f t="shared" si="44"/>
+        <v>#DIV/0!</v>
       </c>
     </row>
     <row r="27" spans="1:33" s="25" customFormat="1" x14ac:dyDescent="0.2">
@@ -3192,61 +3220,64 @@
       <c r="E29" s="6"/>
       <c r="F29" s="6"/>
       <c r="G29" s="28">
-        <f t="shared" ref="G29:I29" si="44">+G3/C3-1</f>
+        <f t="shared" ref="G29:I29" si="45">+G3/C3-1</f>
         <v>-1.8069973087274094E-2</v>
       </c>
       <c r="H29" s="28">
-        <f t="shared" si="44"/>
+        <f t="shared" si="45"/>
         <v>-1.967592592592593E-2</v>
       </c>
       <c r="I29" s="28">
-        <f t="shared" si="44"/>
+        <f t="shared" si="45"/>
         <v>-2.0785219399538146E-2</v>
       </c>
       <c r="J29" s="28">
-        <f t="shared" ref="J29:M30" si="45">+J3/F3-1</f>
+        <f t="shared" ref="J29:M30" si="46">+J3/F3-1</f>
         <v>-2.1857923497267784E-2</v>
       </c>
       <c r="K29" s="28">
-        <f t="shared" si="45"/>
+        <f t="shared" si="46"/>
         <v>-2.2709475332811313E-2</v>
       </c>
       <c r="L29" s="28">
-        <f t="shared" si="45"/>
+        <f t="shared" si="46"/>
         <v>-3.9748130657221603E-2</v>
       </c>
       <c r="M29" s="28">
-        <f t="shared" si="45"/>
+        <f t="shared" si="46"/>
         <v>-1.8474842767295607E-2</v>
       </c>
       <c r="N29" s="27"/>
       <c r="O29" s="27"/>
       <c r="P29" s="27"/>
       <c r="Q29" s="28">
-        <f t="shared" ref="Q29:V30" si="46">Q3/P3-1</f>
+        <f t="shared" ref="Q29:W30" si="47">Q3/P3-1</f>
         <v>4.7276142767689322E-2</v>
       </c>
       <c r="R29" s="28">
-        <f t="shared" si="46"/>
+        <f t="shared" si="47"/>
         <v>-0.15246636771300448</v>
       </c>
       <c r="S29" s="28">
-        <f t="shared" si="46"/>
+        <f t="shared" si="47"/>
         <v>-5.2910052910052907E-2</v>
       </c>
       <c r="T29" s="28">
-        <f t="shared" si="46"/>
+        <f t="shared" si="47"/>
         <v>0</v>
       </c>
       <c r="U29" s="28">
-        <f t="shared" si="46"/>
+        <f t="shared" si="47"/>
         <v>-4.5810055865921795E-2</v>
       </c>
       <c r="V29" s="28">
-        <f t="shared" si="46"/>
+        <f t="shared" si="47"/>
         <v>-2.1857923497267784E-2</v>
       </c>
-      <c r="W29" s="27"/>
+      <c r="W29" s="28">
+        <f t="shared" si="47"/>
+        <v>-1</v>
+      </c>
       <c r="X29" s="27"/>
       <c r="Y29" s="27"/>
       <c r="Z29" s="27"/>
@@ -3267,61 +3298,64 @@
       <c r="E30" s="6"/>
       <c r="F30" s="6"/>
       <c r="G30" s="28">
-        <f t="shared" ref="G30:I30" si="47">+G4/C4-1</f>
+        <f t="shared" ref="G30:I30" si="48">+G4/C4-1</f>
         <v>0.19366197183098599</v>
       </c>
       <c r="H30" s="28">
-        <f t="shared" si="47"/>
+        <f t="shared" si="48"/>
         <v>0.18865740740740744</v>
       </c>
       <c r="I30" s="28">
-        <f t="shared" si="47"/>
+        <f t="shared" si="48"/>
         <v>0.13262032085561493</v>
       </c>
       <c r="J30" s="28">
-        <f t="shared" si="45"/>
+        <f t="shared" si="46"/>
         <v>6.5130260521041983E-2</v>
       </c>
       <c r="K30" s="28">
-        <f t="shared" si="45"/>
+        <f t="shared" si="46"/>
         <v>-1.6715830875122961E-2</v>
       </c>
       <c r="L30" s="28">
-        <f t="shared" si="45"/>
+        <f t="shared" si="46"/>
         <v>0.2512171372930867</v>
       </c>
       <c r="M30" s="28">
-        <f t="shared" si="45"/>
+        <f t="shared" si="46"/>
         <v>-5.5712936732766782E-2</v>
       </c>
       <c r="N30" s="27"/>
       <c r="O30" s="27"/>
       <c r="P30" s="27"/>
       <c r="Q30" s="28">
-        <f t="shared" si="46"/>
+        <f t="shared" si="47"/>
         <v>0.21610169491525433</v>
       </c>
       <c r="R30" s="28">
-        <f t="shared" si="46"/>
+        <f t="shared" si="47"/>
         <v>-1.7421602787456414E-2</v>
       </c>
       <c r="S30" s="28">
-        <f t="shared" si="46"/>
+        <f t="shared" si="47"/>
         <v>0.18262411347517737</v>
       </c>
       <c r="T30" s="28">
-        <f t="shared" si="46"/>
+        <f t="shared" si="47"/>
         <v>0</v>
       </c>
       <c r="U30" s="28">
-        <f t="shared" si="46"/>
+        <f t="shared" si="47"/>
         <v>0.49625187406296845</v>
       </c>
       <c r="V30" s="28">
-        <f t="shared" si="46"/>
+        <f t="shared" si="47"/>
         <v>6.5130260521041983E-2</v>
       </c>
-      <c r="W30" s="27"/>
+      <c r="W30" s="28">
+        <f t="shared" si="47"/>
+        <v>-1</v>
+      </c>
       <c r="X30" s="27"/>
       <c r="Y30" s="27"/>
       <c r="Z30" s="27"/>
@@ -3342,61 +3376,64 @@
       <c r="E31" s="6"/>
       <c r="F31" s="6"/>
       <c r="G31" s="28">
-        <f t="shared" ref="G31:G34" si="48">+G8/C8-1</f>
+        <f t="shared" ref="G31:G34" si="49">+G8/C8-1</f>
         <v>4.8140043763676088E-2</v>
       </c>
       <c r="H31" s="28">
-        <f t="shared" ref="H31:H34" si="49">+H8/D8-1</f>
+        <f t="shared" ref="H31:H34" si="50">+H8/D8-1</f>
         <v>8.2610912799591985E-2</v>
       </c>
       <c r="I31" s="28">
-        <f t="shared" ref="I31:I34" si="50">+I8/E8-1</f>
+        <f t="shared" ref="I31:I34" si="51">+I8/E8-1</f>
         <v>1.1288805268109048E-2</v>
       </c>
       <c r="J31" s="28">
-        <f t="shared" ref="J31:M33" si="51">+J8/F8-1</f>
+        <f t="shared" ref="J31:M33" si="52">+J8/F8-1</f>
         <v>-3.321678321678323E-2</v>
       </c>
       <c r="K31" s="28">
-        <f t="shared" si="51"/>
+        <f t="shared" si="52"/>
         <v>3.3924843423799533E-2</v>
       </c>
       <c r="L31" s="28">
-        <f t="shared" si="51"/>
+        <f t="shared" si="52"/>
         <v>1.2717852096090443E-2</v>
       </c>
       <c r="M31" s="28">
-        <f t="shared" si="51"/>
+        <f t="shared" si="52"/>
         <v>4.7906976744185981E-2</v>
       </c>
       <c r="N31" s="27"/>
       <c r="O31" s="27"/>
       <c r="P31" s="27"/>
       <c r="Q31" s="28" t="e">
-        <f t="shared" ref="Q31:U33" si="52">+Q8/P8-1</f>
+        <f t="shared" ref="Q31:U33" si="53">+Q8/P8-1</f>
         <v>#DIV/0!</v>
       </c>
       <c r="R31" s="28" t="e">
-        <f t="shared" si="52"/>
+        <f t="shared" si="53"/>
         <v>#DIV/0!</v>
       </c>
       <c r="S31" s="28" t="e">
-        <f t="shared" si="52"/>
+        <f t="shared" si="53"/>
         <v>#DIV/0!</v>
       </c>
       <c r="T31" s="28" t="e">
-        <f t="shared" si="52"/>
+        <f t="shared" si="53"/>
         <v>#DIV/0!</v>
       </c>
       <c r="U31" s="28">
-        <f t="shared" si="52"/>
+        <f t="shared" si="53"/>
         <v>-3.764877337867345E-3</v>
       </c>
       <c r="V31" s="28">
-        <f t="shared" ref="V31:V33" si="53">+V8/U8-1</f>
+        <f t="shared" ref="V31:W33" si="54">+V8/U8-1</f>
         <v>2.4137510666829121E-2</v>
       </c>
-      <c r="W31" s="27"/>
+      <c r="W31" s="28">
+        <f t="shared" si="54"/>
+        <v>-1</v>
+      </c>
       <c r="X31" s="27"/>
       <c r="Y31" s="27"/>
       <c r="Z31" s="27"/>
@@ -3417,61 +3454,64 @@
       <c r="E32" s="6"/>
       <c r="F32" s="6"/>
       <c r="G32" s="28">
-        <f t="shared" si="48"/>
+        <f t="shared" si="49"/>
         <v>-4.3352601156069204E-3</v>
       </c>
       <c r="H32" s="28">
-        <f t="shared" si="49"/>
+        <f t="shared" si="50"/>
         <v>1.4569536423840956E-2</v>
       </c>
       <c r="I32" s="28">
-        <f t="shared" si="50"/>
+        <f t="shared" si="51"/>
         <v>1.3528748590755368E-2</v>
       </c>
       <c r="J32" s="28">
-        <f t="shared" si="51"/>
+        <f t="shared" si="52"/>
         <v>-2.6812313803376342E-2</v>
       </c>
       <c r="K32" s="28">
-        <f t="shared" si="51"/>
+        <f t="shared" si="52"/>
         <v>5.079825834542806E-2</v>
       </c>
       <c r="L32" s="28">
-        <f t="shared" si="51"/>
+        <f t="shared" si="52"/>
         <v>7.8328981723236879E-3</v>
       </c>
       <c r="M32" s="28">
-        <f t="shared" si="51"/>
+        <f t="shared" si="52"/>
         <v>5.784204671857629E-2</v>
       </c>
       <c r="N32" s="27"/>
       <c r="O32" s="27"/>
       <c r="P32" s="27"/>
       <c r="Q32" s="28" t="e">
-        <f t="shared" si="52"/>
+        <f t="shared" si="53"/>
         <v>#DIV/0!</v>
       </c>
       <c r="R32" s="28" t="e">
-        <f t="shared" si="52"/>
+        <f t="shared" si="53"/>
         <v>#DIV/0!</v>
       </c>
       <c r="S32" s="28" t="e">
-        <f t="shared" si="52"/>
+        <f t="shared" si="53"/>
         <v>#DIV/0!</v>
       </c>
       <c r="T32" s="28" t="e">
-        <f t="shared" si="52"/>
+        <f t="shared" si="53"/>
         <v>#DIV/0!</v>
       </c>
       <c r="U32" s="28">
-        <f t="shared" si="52"/>
+        <f t="shared" si="53"/>
         <v>-0.11473237943826176</v>
       </c>
       <c r="V32" s="28">
-        <f t="shared" si="53"/>
+        <f t="shared" si="54"/>
         <v>-2.0951810835079243E-3</v>
       </c>
-      <c r="W32" s="27"/>
+      <c r="W32" s="28">
+        <f t="shared" si="54"/>
+        <v>-1</v>
+      </c>
       <c r="X32" s="27"/>
       <c r="Y32" s="27"/>
       <c r="Z32" s="27"/>
@@ -3492,61 +3532,64 @@
       <c r="E33" s="6"/>
       <c r="F33" s="6"/>
       <c r="G33" s="28">
-        <f t="shared" si="48"/>
+        <f t="shared" si="49"/>
         <v>1.8518518518518601E-2</v>
       </c>
       <c r="H33" s="28">
-        <f t="shared" si="49"/>
+        <f t="shared" si="50"/>
         <v>-2.0833333333333259E-3</v>
       </c>
       <c r="I33" s="28">
-        <f t="shared" si="50"/>
+        <f t="shared" si="51"/>
         <v>1.9565217391304346E-2</v>
       </c>
       <c r="J33" s="28">
-        <f t="shared" si="51"/>
+        <f t="shared" si="52"/>
         <v>6.7019400352733793E-2</v>
       </c>
       <c r="K33" s="28">
-        <f t="shared" si="51"/>
+        <f t="shared" si="52"/>
         <v>-2.7272727272727226E-2</v>
       </c>
       <c r="L33" s="28">
-        <f t="shared" si="51"/>
+        <f t="shared" si="52"/>
         <v>-8.3507306889353261E-3</v>
       </c>
       <c r="M33" s="28">
-        <f t="shared" si="51"/>
+        <f t="shared" si="52"/>
         <v>-1.0660980810234588E-2</v>
       </c>
       <c r="N33" s="27"/>
       <c r="O33" s="27"/>
       <c r="P33" s="27"/>
       <c r="Q33" s="28" t="e">
-        <f t="shared" si="52"/>
+        <f t="shared" si="53"/>
         <v>#DIV/0!</v>
       </c>
       <c r="R33" s="28" t="e">
-        <f t="shared" si="52"/>
+        <f t="shared" si="53"/>
         <v>#DIV/0!</v>
       </c>
       <c r="S33" s="28" t="e">
-        <f t="shared" si="52"/>
+        <f t="shared" si="53"/>
         <v>#DIV/0!</v>
       </c>
       <c r="T33" s="28" t="e">
-        <f t="shared" si="52"/>
+        <f t="shared" si="53"/>
         <v>#DIV/0!</v>
       </c>
       <c r="U33" s="28">
-        <f t="shared" si="52"/>
+        <f t="shared" si="53"/>
         <v>-8.364839319470696E-2</v>
       </c>
       <c r="V33" s="28">
-        <f t="shared" si="53"/>
+        <f t="shared" si="54"/>
         <v>2.7849406910778862E-2</v>
       </c>
-      <c r="W33" s="27"/>
+      <c r="W33" s="28">
+        <f t="shared" si="54"/>
+        <v>-1</v>
+      </c>
       <c r="X33" s="27"/>
       <c r="Y33" s="27"/>
       <c r="Z33" s="27"/>
@@ -3567,15 +3610,15 @@
       <c r="E34" s="6"/>
       <c r="F34" s="6"/>
       <c r="G34" s="28">
-        <f t="shared" si="48"/>
+        <f t="shared" si="49"/>
         <v>2.4922118380062308E-2</v>
       </c>
       <c r="H34" s="28">
-        <f t="shared" si="49"/>
+        <f t="shared" si="50"/>
         <v>-8.7976539589442737E-3</v>
       </c>
       <c r="I34" s="28">
-        <f t="shared" si="50"/>
+        <f t="shared" si="51"/>
         <v>3.9426523297491078E-2</v>
       </c>
       <c r="J34" s="28">
@@ -3598,30 +3641,33 @@
       <c r="O34" s="27"/>
       <c r="P34" s="27"/>
       <c r="Q34" s="28" t="e">
-        <f t="shared" ref="Q34:U34" si="54">+Q11/P11-1</f>
+        <f t="shared" ref="Q34:U34" si="55">+Q11/P11-1</f>
         <v>#DIV/0!</v>
       </c>
       <c r="R34" s="28" t="e">
-        <f t="shared" si="54"/>
+        <f t="shared" si="55"/>
         <v>#DIV/0!</v>
       </c>
       <c r="S34" s="28" t="e">
-        <f t="shared" si="54"/>
+        <f t="shared" si="55"/>
         <v>#DIV/0!</v>
       </c>
       <c r="T34" s="28" t="e">
-        <f t="shared" si="54"/>
+        <f t="shared" si="55"/>
         <v>#DIV/0!</v>
       </c>
       <c r="U34" s="28">
-        <f t="shared" si="54"/>
+        <f t="shared" si="55"/>
         <v>-8.108108108108103E-2</v>
       </c>
       <c r="V34" s="28">
         <f>+V11/U11-1</f>
         <v>-5.1470588235293935E-3</v>
       </c>
-      <c r="W34" s="27"/>
+      <c r="W34" s="28">
+        <f>+W11/V11-1</f>
+        <v>-1</v>
+      </c>
       <c r="X34" s="27"/>
       <c r="Y34" s="27"/>
       <c r="Z34" s="27"/>
@@ -3642,61 +3688,64 @@
       <c r="E35" s="27"/>
       <c r="F35" s="27"/>
       <c r="G35" s="28">
-        <f t="shared" ref="G35:G36" si="55">+G13/C13-1</f>
+        <f t="shared" ref="G35:G36" si="56">+G13/C13-1</f>
         <v>2.5815879201169123E-2</v>
       </c>
       <c r="H35" s="28">
-        <f t="shared" ref="H35:H36" si="56">+H13/D13-1</f>
+        <f t="shared" ref="H35:H36" si="57">+H13/D13-1</f>
         <v>3.7285295349811509E-2</v>
       </c>
       <c r="I35" s="28">
-        <f t="shared" ref="I35:I36" si="57">+I13/E13-1</f>
+        <f t="shared" ref="I35:I36" si="58">+I13/E13-1</f>
         <v>-1.8018018018018056E-2</v>
       </c>
       <c r="J35" s="28">
-        <f t="shared" ref="J35:M35" si="58">+J13/F13-1</f>
+        <f t="shared" ref="J35:M35" si="59">+J13/F13-1</f>
         <v>-4.4271844660194182E-2</v>
       </c>
       <c r="K35" s="28">
-        <f t="shared" si="58"/>
+        <f t="shared" si="59"/>
         <v>3.0531813865146695E-3</v>
       </c>
       <c r="L35" s="28">
-        <f t="shared" si="58"/>
+        <f t="shared" si="59"/>
         <v>-1.4539579967689842E-2</v>
       </c>
       <c r="M35" s="28">
-        <f t="shared" si="58"/>
+        <f t="shared" si="59"/>
         <v>3.4512887723896934E-2</v>
       </c>
       <c r="N35" s="27"/>
       <c r="O35" s="27"/>
       <c r="P35" s="27"/>
       <c r="Q35" s="28">
-        <f t="shared" ref="Q35:V37" si="59">Q13/P13-1</f>
+        <f t="shared" ref="Q35:W37" si="60">Q13/P13-1</f>
         <v>-4.4086773967809689E-2</v>
       </c>
       <c r="R35" s="28">
-        <f t="shared" si="59"/>
+        <f t="shared" si="60"/>
         <v>-0.38815682446721977</v>
       </c>
       <c r="S35" s="28">
-        <f t="shared" si="59"/>
+        <f t="shared" si="60"/>
         <v>0.36120712576442426</v>
       </c>
       <c r="T35" s="28">
-        <f t="shared" si="59"/>
+        <f t="shared" si="60"/>
         <v>-5.742748315265167E-2</v>
       </c>
       <c r="U35" s="28">
-        <f t="shared" si="59"/>
+        <f t="shared" si="60"/>
         <v>-3.1602942700238335E-2</v>
       </c>
       <c r="V35" s="28">
-        <f t="shared" si="59"/>
+        <f t="shared" si="60"/>
         <v>-1.4979670447250459E-3</v>
       </c>
-      <c r="W35" s="27"/>
+      <c r="W35" s="28">
+        <f t="shared" si="60"/>
+        <v>-1</v>
+      </c>
       <c r="X35" s="27"/>
       <c r="Y35" s="27"/>
       <c r="Z35" s="27"/>
@@ -3717,15 +3766,15 @@
       <c r="E36" s="27"/>
       <c r="F36" s="27"/>
       <c r="G36" s="28">
-        <f t="shared" si="55"/>
+        <f t="shared" si="56"/>
         <v>4.8242027800490694E-2</v>
       </c>
       <c r="H36" s="28">
-        <f t="shared" si="56"/>
+        <f t="shared" si="57"/>
         <v>5.4263565891472965E-2</v>
       </c>
       <c r="I36" s="28">
-        <f t="shared" si="57"/>
+        <f t="shared" si="58"/>
         <v>7.2423398328690824E-2</v>
       </c>
       <c r="J36" s="28">
@@ -3748,30 +3797,33 @@
       <c r="O36" s="27"/>
       <c r="P36" s="27"/>
       <c r="Q36" s="28">
-        <f t="shared" si="59"/>
+        <f t="shared" si="60"/>
         <v>9.9489109975799961E-2</v>
       </c>
       <c r="R36" s="28">
-        <f t="shared" si="59"/>
+        <f t="shared" si="60"/>
         <v>0.53533871362191254</v>
       </c>
       <c r="S36" s="28">
-        <f t="shared" si="59"/>
+        <f t="shared" si="60"/>
         <v>2.4370818732080357E-2</v>
       </c>
       <c r="T36" s="28">
-        <f t="shared" si="59"/>
+        <f t="shared" si="60"/>
         <v>-7.2461514538951999E-2</v>
       </c>
       <c r="U36" s="28">
-        <f t="shared" si="59"/>
+        <f t="shared" si="60"/>
         <v>-7.0746018440905334E-2</v>
       </c>
       <c r="V36" s="28">
-        <f t="shared" si="59"/>
+        <f t="shared" si="60"/>
         <v>3.8066029226050846E-2</v>
       </c>
-      <c r="W36" s="27"/>
+      <c r="W36" s="28">
+        <f t="shared" si="60"/>
+        <v>-1</v>
+      </c>
       <c r="X36" s="27"/>
       <c r="Y36" s="27"/>
       <c r="Z36" s="27"/>
@@ -3792,61 +3844,64 @@
       <c r="E37" s="29"/>
       <c r="F37" s="29"/>
       <c r="G37" s="30">
-        <f t="shared" ref="G37:M37" si="60">G15/C15-1</f>
+        <f t="shared" ref="G37:M37" si="61">G15/C15-1</f>
         <v>3.4188034188034289E-2</v>
       </c>
       <c r="H37" s="30">
-        <f t="shared" si="60"/>
+        <f t="shared" si="61"/>
         <v>4.8478015783540052E-2</v>
       </c>
       <c r="I37" s="30">
-        <f t="shared" si="60"/>
+        <f t="shared" si="61"/>
         <v>1.6458720467215304E-2</v>
       </c>
       <c r="J37" s="30">
-        <f t="shared" si="60"/>
+        <f t="shared" si="61"/>
         <v>-3.4667287110283884E-2</v>
       </c>
       <c r="K37" s="30">
-        <f t="shared" si="60"/>
+        <f t="shared" si="61"/>
         <v>2.2136953955135708E-2</v>
       </c>
       <c r="L37" s="30">
-        <f t="shared" si="60"/>
+        <f t="shared" si="61"/>
         <v>1.3440860215054862E-3</v>
       </c>
       <c r="M37" s="30">
-        <f t="shared" si="60"/>
+        <f t="shared" si="61"/>
         <v>2.9511621833376855E-2</v>
       </c>
       <c r="N37" s="29"/>
       <c r="O37" s="29"/>
       <c r="P37" s="29"/>
       <c r="Q37" s="30">
-        <f t="shared" si="59"/>
+        <f t="shared" si="60"/>
         <v>-1.1881785283474056E-2</v>
       </c>
       <c r="R37" s="30">
-        <f t="shared" si="59"/>
+        <f t="shared" si="60"/>
         <v>-0.15766343160593299</v>
       </c>
       <c r="S37" s="30">
-        <f t="shared" si="59"/>
+        <f t="shared" si="60"/>
         <v>0.20797101449275357</v>
       </c>
       <c r="T37" s="30">
-        <f t="shared" si="59"/>
+        <f t="shared" si="60"/>
         <v>-6.3227354529094226E-2</v>
       </c>
       <c r="U37" s="30">
-        <f t="shared" si="59"/>
+        <f t="shared" si="60"/>
         <v>-4.6554815573770503E-2</v>
       </c>
       <c r="V37" s="30">
-        <f t="shared" si="59"/>
+        <f t="shared" si="60"/>
         <v>1.3231244542951215E-2</v>
       </c>
-      <c r="W37" s="27"/>
+      <c r="W37" s="30">
+        <f t="shared" si="60"/>
+        <v>1.8560254540633592E-2</v>
+      </c>
       <c r="X37" s="27"/>
       <c r="Y37" s="27"/>
       <c r="Z37" s="27"/>
@@ -3863,77 +3918,80 @@
         <v>34</v>
       </c>
       <c r="C38" s="28">
-        <f t="shared" ref="C38:J38" si="61">C17/C15</f>
+        <f t="shared" ref="C38:J38" si="62">C17/C15</f>
         <v>0.37057387057387059</v>
       </c>
       <c r="D38" s="28">
-        <f t="shared" si="61"/>
+        <f t="shared" si="62"/>
         <v>0.37570462232243518</v>
       </c>
       <c r="E38" s="28">
-        <f t="shared" si="61"/>
+        <f t="shared" si="62"/>
         <v>0.41306079108043536</v>
       </c>
       <c r="F38" s="28">
-        <f t="shared" si="61"/>
+        <f t="shared" si="62"/>
         <v>0.3890181479758027</v>
       </c>
       <c r="G38" s="28">
-        <f t="shared" si="61"/>
+        <f t="shared" si="62"/>
         <v>0.41233766233766234</v>
       </c>
       <c r="H38" s="28">
-        <f t="shared" si="61"/>
+        <f t="shared" si="62"/>
         <v>0.42553763440860215</v>
       </c>
       <c r="I38" s="28">
-        <f t="shared" si="61"/>
+        <f t="shared" si="62"/>
         <v>0.42700443980151476</v>
       </c>
       <c r="J38" s="28">
-        <f t="shared" si="61"/>
+        <f t="shared" si="62"/>
         <v>0.38852735598939503</v>
       </c>
       <c r="K38" s="28">
-        <f t="shared" ref="K38:L38" si="62">K17/K15</f>
+        <f t="shared" ref="K38:L38" si="63">K17/K15</f>
         <v>0.41813456540571758</v>
       </c>
       <c r="L38" s="28">
-        <f t="shared" si="62"/>
+        <f t="shared" si="63"/>
         <v>0.41234899328859059</v>
       </c>
       <c r="M38" s="28">
-        <f t="shared" ref="M38" si="63">M17/M15</f>
+        <f t="shared" ref="M38" si="64">M17/M15</f>
         <v>0.42364282090309485</v>
       </c>
       <c r="N38" s="27"/>
       <c r="O38" s="27"/>
       <c r="P38" s="27"/>
       <c r="Q38" s="28">
-        <f t="shared" ref="Q38:V38" si="64">Q17/Q15</f>
+        <f t="shared" ref="Q38:V38" si="65">Q17/Q15</f>
         <v>0.37435146188121832</v>
       </c>
       <c r="R38" s="28">
-        <f t="shared" si="64"/>
+        <f t="shared" si="65"/>
         <v>0.34094202898550724</v>
       </c>
       <c r="S38" s="28">
-        <f t="shared" si="64"/>
+        <f t="shared" si="65"/>
         <v>0.39814037192561486</v>
       </c>
       <c r="T38" s="28">
-        <f t="shared" si="64"/>
+        <f t="shared" si="65"/>
         <v>0.34317366803278687</v>
       </c>
       <c r="U38" s="28">
-        <f t="shared" si="64"/>
+        <f t="shared" si="65"/>
         <v>0.38787023977433005</v>
       </c>
       <c r="V38" s="28">
-        <f t="shared" si="64"/>
+        <f t="shared" si="65"/>
         <v>0.41276680365902163</v>
       </c>
-      <c r="W38" s="27"/>
+      <c r="W38" s="28">
+        <f t="shared" ref="W38" si="66">W17/W15</f>
+        <v>0.40791357542626577</v>
+      </c>
       <c r="X38" s="27"/>
       <c r="Y38" s="27"/>
       <c r="Z38" s="27"/>
@@ -3950,77 +4008,80 @@
         <v>35</v>
       </c>
       <c r="C39" s="28">
-        <f t="shared" ref="C39:J39" si="65">C19/C15</f>
+        <f t="shared" ref="C39:J39" si="67">C19/C15</f>
         <v>-3.0525030525030525E-3</v>
       </c>
       <c r="D39" s="28">
-        <f t="shared" si="65"/>
+        <f t="shared" si="67"/>
         <v>2.987598647125141E-2</v>
       </c>
       <c r="E39" s="28">
-        <f t="shared" si="65"/>
+        <f t="shared" si="67"/>
         <v>6.636580833554552E-2</v>
       </c>
       <c r="F39" s="28">
-        <f t="shared" si="65"/>
+        <f t="shared" si="67"/>
         <v>4.9790600279199626E-2</v>
       </c>
       <c r="G39" s="28">
-        <f t="shared" si="65"/>
+        <f t="shared" si="67"/>
         <v>6.0507674144037779E-2</v>
       </c>
       <c r="H39" s="28">
-        <f t="shared" si="65"/>
+        <f t="shared" si="67"/>
         <v>7.8763440860215056E-2</v>
       </c>
       <c r="I39" s="28">
-        <f t="shared" si="65"/>
+        <f t="shared" si="67"/>
         <v>9.2713502219900754E-2</v>
       </c>
       <c r="J39" s="28">
-        <f t="shared" si="65"/>
+        <f t="shared" si="67"/>
         <v>6.2424680645938778E-2</v>
       </c>
       <c r="K39" s="28">
-        <f t="shared" ref="K39:L39" si="66">K19/K15</f>
+        <f t="shared" ref="K39:L39" si="68">K19/K15</f>
         <v>7.5079410915391276E-2</v>
       </c>
       <c r="L39" s="28">
-        <f t="shared" si="66"/>
+        <f t="shared" si="68"/>
         <v>7.8389261744966438E-2</v>
       </c>
       <c r="M39" s="28">
-        <f t="shared" ref="M39" si="67">M19/M15</f>
+        <f t="shared" ref="M39" si="69">M19/M15</f>
         <v>8.472856418061897E-2</v>
       </c>
       <c r="N39" s="27"/>
       <c r="O39" s="27"/>
       <c r="P39" s="27"/>
       <c r="Q39" s="28">
-        <f t="shared" ref="Q39:V39" si="68">Q19/Q15</f>
+        <f t="shared" ref="Q39:V39" si="70">Q19/Q15</f>
         <v>3.5036318134651773E-2</v>
       </c>
       <c r="R39" s="28">
-        <f t="shared" si="68"/>
+        <f t="shared" si="70"/>
         <v>-6.246376811594203E-2</v>
       </c>
       <c r="S39" s="28">
-        <f t="shared" si="68"/>
+        <f t="shared" si="70"/>
         <v>4.8590281943611278E-2</v>
       </c>
       <c r="T39" s="28">
-        <f t="shared" si="68"/>
+        <f t="shared" si="70"/>
         <v>-4.4185450819672128E-3</v>
       </c>
       <c r="U39" s="28">
-        <f t="shared" si="68"/>
+        <f t="shared" si="70"/>
         <v>3.7611659614480486E-2</v>
       </c>
       <c r="V39" s="28">
-        <f t="shared" si="68"/>
+        <f t="shared" si="70"/>
         <v>7.3710725175659547E-2</v>
       </c>
-      <c r="W39" s="27"/>
+      <c r="W39" s="28">
+        <f t="shared" ref="W39" si="71">W19/W15</f>
+        <v>7.2562800989196929E-2</v>
+      </c>
       <c r="X39" s="27"/>
       <c r="Y39" s="27"/>
       <c r="Z39" s="27"/>
@@ -4038,73 +4099,76 @@
       </c>
       <c r="C40" s="28"/>
       <c r="D40" s="28">
-        <f t="shared" ref="D40:J40" si="69">(D19-C19)/(D17-C17)</f>
+        <f t="shared" ref="D40:J40" si="72">(D19-C19)/(D17-C17)</f>
         <v>0.97478991596638653</v>
       </c>
       <c r="E40" s="28">
-        <f t="shared" si="69"/>
+        <f t="shared" si="72"/>
         <v>0.64573991031390132</v>
       </c>
       <c r="F40" s="28">
-        <f t="shared" si="69"/>
+        <f t="shared" si="72"/>
         <v>-0.31034482758620691</v>
       </c>
       <c r="G40" s="28">
-        <f t="shared" si="69"/>
+        <f t="shared" si="72"/>
         <v>3.272727272727273E-2</v>
       </c>
       <c r="H40" s="28">
-        <f t="shared" si="69"/>
+        <f t="shared" si="72"/>
         <v>0.4731182795698925</v>
       </c>
       <c r="I40" s="28">
-        <f t="shared" si="69"/>
+        <f t="shared" si="72"/>
         <v>1.1923076923076923</v>
       </c>
       <c r="J40" s="28">
-        <f t="shared" si="69"/>
+        <f t="shared" si="72"/>
         <v>4.1739130434782608</v>
       </c>
       <c r="K40" s="28">
-        <f t="shared" ref="K40:M40" si="70">(K19-J19)/(K17-J17)</f>
+        <f t="shared" ref="K40:M40" si="73">(K19-J19)/(K17-J17)</f>
         <v>-6.0975609756097563E-3</v>
       </c>
       <c r="L40" s="28">
-        <f t="shared" si="70"/>
+        <f t="shared" si="73"/>
         <v>0.36363636363636365</v>
       </c>
       <c r="M40" s="28">
-        <f t="shared" si="70"/>
+        <f t="shared" si="73"/>
         <v>0.31343283582089554</v>
       </c>
       <c r="N40" s="27"/>
       <c r="O40" s="27"/>
       <c r="P40" s="27"/>
       <c r="Q40" s="28">
-        <f t="shared" ref="Q40:V40" si="71">(Q19-P19)/(Q15-P15)</f>
+        <f t="shared" ref="Q40:W40" si="74">(Q19-P19)/(Q15-P15)</f>
         <v>4</v>
       </c>
       <c r="R40" s="28">
-        <f t="shared" si="71"/>
+        <f t="shared" si="74"/>
         <v>0.55594270228416565</v>
       </c>
       <c r="S40" s="28">
-        <f t="shared" si="71"/>
+        <f t="shared" si="74"/>
         <v>0.58257839721254356</v>
       </c>
       <c r="T40" s="28">
-        <f t="shared" si="71"/>
+        <f t="shared" si="74"/>
         <v>0.83396584440227706</v>
       </c>
       <c r="U40" s="28">
-        <f t="shared" si="71"/>
+        <f t="shared" si="74"/>
         <v>-0.86519944979367258</v>
       </c>
       <c r="V40" s="28">
-        <f t="shared" si="71"/>
+        <f t="shared" si="74"/>
         <v>2.8020304568527918</v>
       </c>
-      <c r="W40" s="27"/>
+      <c r="W40" s="28">
+        <f t="shared" si="74"/>
+        <v>1.0714285714285714E-2</v>
+      </c>
       <c r="X40" s="27"/>
       <c r="Y40" s="27"/>
       <c r="Z40" s="27"/>
@@ -4121,77 +4185,80 @@
         <v>36</v>
       </c>
       <c r="C41" s="28">
-        <f t="shared" ref="C41:J41" si="72">C23/C22</f>
+        <f t="shared" ref="C41:J41" si="75">C23/C22</f>
         <v>0.1</v>
       </c>
       <c r="D41" s="28">
-        <f t="shared" si="72"/>
+        <f t="shared" si="75"/>
         <v>-8.3333333333333329E-2</v>
       </c>
       <c r="E41" s="28">
-        <f t="shared" si="72"/>
+        <f t="shared" si="75"/>
         <v>0.128</v>
       </c>
       <c r="F41" s="28">
-        <f t="shared" si="72"/>
+        <f t="shared" si="75"/>
         <v>0.15137614678899083</v>
       </c>
       <c r="G41" s="28">
-        <f t="shared" si="72"/>
+        <f t="shared" si="75"/>
         <v>0.24038461538461539</v>
       </c>
       <c r="H41" s="28">
-        <f t="shared" si="72"/>
+        <f t="shared" si="75"/>
         <v>0.30405405405405406</v>
       </c>
       <c r="I41" s="28">
-        <f t="shared" si="72"/>
+        <f t="shared" si="75"/>
         <v>0.24099722991689751</v>
       </c>
       <c r="J41" s="28">
-        <f t="shared" si="72"/>
+        <f t="shared" si="75"/>
         <v>0.24264705882352941</v>
       </c>
       <c r="K41" s="28">
-        <f t="shared" ref="K41:L41" si="73">K23/K22</f>
+        <f t="shared" ref="K41:L41" si="76">K23/K22</f>
         <v>0.26615969581749049</v>
       </c>
       <c r="L41" s="28">
-        <f t="shared" si="73"/>
+        <f t="shared" si="76"/>
         <v>0.27027027027027029</v>
       </c>
       <c r="M41" s="28">
-        <f t="shared" ref="M41" si="74">M23/M22</f>
+        <f t="shared" ref="M41" si="77">M23/M22</f>
         <v>0.29970326409495551</v>
       </c>
       <c r="N41" s="27"/>
       <c r="O41" s="27"/>
       <c r="P41" s="27"/>
       <c r="Q41" s="28">
-        <f t="shared" ref="Q41:V41" si="75">Q23/Q22</f>
+        <f t="shared" ref="Q41:V41" si="78">Q23/Q22</f>
         <v>0.33522727272727271</v>
       </c>
       <c r="R41" s="28">
-        <f t="shared" si="75"/>
+        <f t="shared" si="78"/>
         <v>0.39655172413793105</v>
       </c>
       <c r="S41" s="28">
-        <f t="shared" si="75"/>
+        <f t="shared" si="78"/>
         <v>0.20743034055727555</v>
       </c>
       <c r="T41" s="28">
-        <f t="shared" si="75"/>
+        <f t="shared" si="78"/>
         <v>-0.45323741007194246</v>
       </c>
       <c r="U41" s="28">
-        <f t="shared" si="75"/>
+        <f t="shared" si="78"/>
         <v>9.7122302158273388E-2</v>
       </c>
       <c r="V41" s="28">
-        <f t="shared" si="75"/>
+        <f t="shared" si="78"/>
         <v>0.25769569041336854</v>
       </c>
-      <c r="W41" s="27"/>
+      <c r="W41" s="28">
+        <f t="shared" ref="W41" si="79">W23/W22</f>
+        <v>0.27915194346289751</v>
+      </c>
       <c r="X41" s="27"/>
       <c r="Y41" s="27"/>
       <c r="Z41" s="27"/>
@@ -4464,31 +4531,31 @@
         <v>4283</v>
       </c>
       <c r="D48" s="6">
-        <f t="shared" ref="D48:J48" si="76">SUM(D44:D47)</f>
+        <f t="shared" ref="D48:J48" si="80">SUM(D44:D47)</f>
         <v>0</v>
       </c>
       <c r="E48" s="6">
-        <f t="shared" si="76"/>
+        <f t="shared" si="80"/>
         <v>0</v>
       </c>
       <c r="F48" s="6">
-        <f t="shared" si="76"/>
+        <f t="shared" si="80"/>
         <v>1902</v>
       </c>
       <c r="G48" s="6">
-        <f t="shared" si="76"/>
+        <f t="shared" si="80"/>
         <v>4197</v>
       </c>
       <c r="H48" s="6">
-        <f t="shared" si="76"/>
+        <f t="shared" si="80"/>
         <v>0</v>
       </c>
       <c r="I48" s="6">
-        <f t="shared" si="76"/>
+        <f t="shared" si="80"/>
         <v>0</v>
       </c>
       <c r="J48" s="6">
-        <f t="shared" si="76"/>
+        <f t="shared" si="80"/>
         <v>0</v>
       </c>
       <c r="K48" s="6"/>
@@ -4497,31 +4564,31 @@
       <c r="N48" s="6"/>
       <c r="O48" s="6"/>
       <c r="P48" s="6">
-        <f t="shared" ref="P48" si="77">SUM(P44:P47)</f>
+        <f t="shared" ref="P48" si="81">SUM(P44:P47)</f>
         <v>0</v>
       </c>
       <c r="Q48" s="6">
-        <f t="shared" ref="Q48" si="78">SUM(Q44:Q47)</f>
+        <f t="shared" ref="Q48" si="82">SUM(Q44:Q47)</f>
         <v>0</v>
       </c>
       <c r="R48" s="6">
-        <f t="shared" ref="R48" si="79">SUM(R44:R47)</f>
+        <f t="shared" ref="R48" si="83">SUM(R44:R47)</f>
         <v>0</v>
       </c>
       <c r="S48" s="6">
-        <f t="shared" ref="S48" si="80">SUM(S44:S47)</f>
+        <f t="shared" ref="S48" si="84">SUM(S44:S47)</f>
         <v>0</v>
       </c>
       <c r="T48" s="6">
-        <f t="shared" ref="T48" si="81">SUM(T44:T47)</f>
+        <f t="shared" ref="T48" si="85">SUM(T44:T47)</f>
         <v>4617</v>
       </c>
       <c r="U48" s="6">
-        <f t="shared" ref="U48:V48" si="82">SUM(U44:U47)</f>
+        <f t="shared" ref="U48:V48" si="86">SUM(U44:U47)</f>
         <v>4395</v>
       </c>
       <c r="V48" s="6">
-        <f t="shared" si="82"/>
+        <f t="shared" si="86"/>
         <v>5203</v>
       </c>
       <c r="W48" s="27"/>
@@ -4683,31 +4750,31 @@
         <v>6649</v>
       </c>
       <c r="D52" s="6">
-        <f t="shared" ref="D52:J52" si="83">SUM(D49:D51)</f>
+        <f t="shared" ref="D52:J52" si="87">SUM(D49:D51)</f>
         <v>0</v>
       </c>
       <c r="E52" s="6">
-        <f t="shared" si="83"/>
+        <f t="shared" si="87"/>
         <v>0</v>
       </c>
       <c r="F52" s="6">
-        <f t="shared" si="83"/>
+        <f t="shared" si="87"/>
         <v>0</v>
       </c>
       <c r="G52" s="6">
-        <f t="shared" si="83"/>
+        <f t="shared" si="87"/>
         <v>6711</v>
       </c>
       <c r="H52" s="6">
-        <f t="shared" si="83"/>
+        <f t="shared" si="87"/>
         <v>0</v>
       </c>
       <c r="I52" s="6">
-        <f t="shared" si="83"/>
+        <f t="shared" si="87"/>
         <v>0</v>
       </c>
       <c r="J52" s="6">
-        <f t="shared" si="83"/>
+        <f t="shared" si="87"/>
         <v>0</v>
       </c>
       <c r="K52" s="6"/>
@@ -4716,31 +4783,31 @@
       <c r="N52" s="6"/>
       <c r="O52" s="6"/>
       <c r="P52" s="6">
-        <f t="shared" ref="P52" si="84">SUM(P49:P51)</f>
+        <f t="shared" ref="P52" si="88">SUM(P49:P51)</f>
         <v>0</v>
       </c>
       <c r="Q52" s="6">
-        <f t="shared" ref="Q52" si="85">SUM(Q49:Q51)</f>
+        <f t="shared" ref="Q52" si="89">SUM(Q49:Q51)</f>
         <v>0</v>
       </c>
       <c r="R52" s="6">
-        <f t="shared" ref="R52" si="86">SUM(R49:R51)</f>
+        <f t="shared" ref="R52" si="90">SUM(R49:R51)</f>
         <v>0</v>
       </c>
       <c r="S52" s="6">
-        <f t="shared" ref="S52" si="87">SUM(S49:S51)</f>
+        <f t="shared" ref="S52" si="91">SUM(S49:S51)</f>
         <v>0</v>
       </c>
       <c r="T52" s="6">
-        <f t="shared" ref="T52" si="88">SUM(T49:T51)</f>
+        <f t="shared" ref="T52" si="92">SUM(T49:T51)</f>
         <v>6769</v>
       </c>
       <c r="U52" s="6">
-        <f t="shared" ref="U52" si="89">SUM(U49:U51)</f>
+        <f t="shared" ref="U52" si="93">SUM(U49:U51)</f>
         <v>6649</v>
       </c>
       <c r="V52" s="6">
-        <f t="shared" ref="V52" si="90">SUM(V49:V51)</f>
+        <f t="shared" ref="V52" si="94">SUM(V49:V51)</f>
         <v>6682</v>
       </c>
       <c r="W52" s="27"/>
@@ -4760,35 +4827,35 @@
         <v>47</v>
       </c>
       <c r="C53" s="24">
-        <f t="shared" ref="C53:J53" si="91">C52+C48</f>
+        <f t="shared" ref="C53:J53" si="95">C52+C48</f>
         <v>10932</v>
       </c>
       <c r="D53" s="24">
-        <f t="shared" si="91"/>
+        <f t="shared" si="95"/>
         <v>0</v>
       </c>
       <c r="E53" s="24">
-        <f t="shared" si="91"/>
+        <f t="shared" si="95"/>
         <v>0</v>
       </c>
       <c r="F53" s="24">
-        <f t="shared" si="91"/>
+        <f t="shared" si="95"/>
         <v>1902</v>
       </c>
       <c r="G53" s="24">
-        <f t="shared" si="91"/>
+        <f t="shared" si="95"/>
         <v>10908</v>
       </c>
       <c r="H53" s="24">
-        <f t="shared" si="91"/>
+        <f t="shared" si="95"/>
         <v>0</v>
       </c>
       <c r="I53" s="24">
-        <f t="shared" si="91"/>
+        <f t="shared" si="95"/>
         <v>0</v>
       </c>
       <c r="J53" s="24">
-        <f t="shared" si="91"/>
+        <f t="shared" si="95"/>
         <v>0</v>
       </c>
       <c r="K53" s="24"/>
@@ -4797,31 +4864,31 @@
       <c r="N53" s="6"/>
       <c r="O53" s="6"/>
       <c r="P53" s="24">
-        <f t="shared" ref="P53:V53" si="92">P52+P48</f>
+        <f t="shared" ref="P53:V53" si="96">P52+P48</f>
         <v>0</v>
       </c>
       <c r="Q53" s="24">
-        <f t="shared" si="92"/>
+        <f t="shared" si="96"/>
         <v>0</v>
       </c>
       <c r="R53" s="24">
-        <f t="shared" si="92"/>
+        <f t="shared" si="96"/>
         <v>0</v>
       </c>
       <c r="S53" s="24">
-        <f t="shared" si="92"/>
+        <f t="shared" si="96"/>
         <v>0</v>
       </c>
       <c r="T53" s="24">
-        <f t="shared" si="92"/>
+        <f t="shared" si="96"/>
         <v>11386</v>
       </c>
       <c r="U53" s="24">
-        <f t="shared" si="92"/>
+        <f t="shared" si="96"/>
         <v>11044</v>
       </c>
       <c r="V53" s="24">
-        <f t="shared" si="92"/>
+        <f t="shared" si="96"/>
         <v>11885</v>
       </c>
       <c r="W53" s="27"/>
@@ -5029,31 +5096,31 @@
         <v>2918</v>
       </c>
       <c r="D58" s="6">
-        <f t="shared" ref="D58:J58" si="93">SUM(D54:D57)</f>
+        <f t="shared" ref="D58:J58" si="97">SUM(D54:D57)</f>
         <v>0</v>
       </c>
       <c r="E58" s="6">
-        <f t="shared" si="93"/>
+        <f t="shared" si="97"/>
         <v>0</v>
       </c>
       <c r="F58" s="6">
-        <f t="shared" si="93"/>
+        <f t="shared" si="97"/>
         <v>0</v>
       </c>
       <c r="G58" s="6">
-        <f t="shared" si="93"/>
+        <f t="shared" si="97"/>
         <v>2806</v>
       </c>
       <c r="H58" s="6">
-        <f t="shared" si="93"/>
+        <f t="shared" si="97"/>
         <v>0</v>
       </c>
       <c r="I58" s="6">
-        <f t="shared" si="93"/>
+        <f t="shared" si="97"/>
         <v>0</v>
       </c>
       <c r="J58" s="6">
-        <f t="shared" si="93"/>
+        <f t="shared" si="97"/>
         <v>0</v>
       </c>
       <c r="K58" s="6"/>
@@ -5062,31 +5129,31 @@
       <c r="N58" s="6"/>
       <c r="O58" s="6"/>
       <c r="P58" s="6">
-        <f t="shared" ref="P58" si="94">SUM(P54:P57)</f>
+        <f t="shared" ref="P58" si="98">SUM(P54:P57)</f>
         <v>0</v>
       </c>
       <c r="Q58" s="6">
-        <f t="shared" ref="Q58" si="95">SUM(Q54:Q57)</f>
+        <f t="shared" ref="Q58" si="99">SUM(Q54:Q57)</f>
         <v>0</v>
       </c>
       <c r="R58" s="6">
-        <f t="shared" ref="R58" si="96">SUM(R54:R57)</f>
+        <f t="shared" ref="R58" si="100">SUM(R54:R57)</f>
         <v>0</v>
       </c>
       <c r="S58" s="6">
-        <f t="shared" ref="S58" si="97">SUM(S54:S57)</f>
+        <f t="shared" ref="S58" si="101">SUM(S54:S57)</f>
         <v>0</v>
       </c>
       <c r="T58" s="6">
-        <f t="shared" ref="T58" si="98">SUM(T54:T57)</f>
+        <f t="shared" ref="T58" si="102">SUM(T54:T57)</f>
         <v>3256</v>
       </c>
       <c r="U58" s="6">
-        <f t="shared" ref="U58" si="99">SUM(U54:U57)</f>
+        <f t="shared" ref="U58" si="103">SUM(U54:U57)</f>
         <v>3096</v>
       </c>
       <c r="V58" s="6">
-        <f t="shared" ref="V58" si="100">SUM(V54:V57)</f>
+        <f t="shared" ref="V58" si="104">SUM(V54:V57)</f>
         <v>3256</v>
       </c>
       <c r="W58" s="27"/>
@@ -5294,31 +5361,31 @@
         <v>5829</v>
       </c>
       <c r="D63" s="6">
-        <f t="shared" ref="D63:J63" si="101">SUM(D59:D62)</f>
+        <f t="shared" ref="D63:J63" si="105">SUM(D59:D62)</f>
         <v>0</v>
       </c>
       <c r="E63" s="6">
-        <f t="shared" si="101"/>
+        <f t="shared" si="105"/>
         <v>0</v>
       </c>
       <c r="F63" s="6">
-        <f t="shared" si="101"/>
+        <f t="shared" si="105"/>
         <v>0</v>
       </c>
       <c r="G63" s="6">
-        <f t="shared" si="101"/>
+        <f t="shared" si="105"/>
         <v>5395</v>
       </c>
       <c r="H63" s="6">
-        <f t="shared" si="101"/>
+        <f t="shared" si="105"/>
         <v>0</v>
       </c>
       <c r="I63" s="6">
-        <f t="shared" si="101"/>
+        <f t="shared" si="105"/>
         <v>0</v>
       </c>
       <c r="J63" s="6">
-        <f t="shared" si="101"/>
+        <f t="shared" si="105"/>
         <v>0</v>
       </c>
       <c r="K63" s="6"/>
@@ -5327,31 +5394,31 @@
       <c r="N63" s="6"/>
       <c r="O63" s="6"/>
       <c r="P63" s="6">
-        <f t="shared" ref="P63" si="102">SUM(P59:P62)</f>
+        <f t="shared" ref="P63" si="106">SUM(P59:P62)</f>
         <v>0</v>
       </c>
       <c r="Q63" s="6">
-        <f t="shared" ref="Q63" si="103">SUM(Q59:Q62)</f>
+        <f t="shared" ref="Q63" si="107">SUM(Q59:Q62)</f>
         <v>0</v>
       </c>
       <c r="R63" s="6">
-        <f t="shared" ref="R63" si="104">SUM(R59:R62)</f>
+        <f t="shared" ref="R63" si="108">SUM(R59:R62)</f>
         <v>0</v>
       </c>
       <c r="S63" s="6">
-        <f t="shared" ref="S63" si="105">SUM(S59:S62)</f>
+        <f t="shared" ref="S63" si="109">SUM(S59:S62)</f>
         <v>0</v>
       </c>
       <c r="T63" s="6">
-        <f t="shared" ref="T63" si="106">SUM(T59:T62)</f>
+        <f t="shared" ref="T63" si="110">SUM(T59:T62)</f>
         <v>5897</v>
       </c>
       <c r="U63" s="6">
-        <f t="shared" ref="U63" si="107">SUM(U59:U62)</f>
+        <f t="shared" ref="U63" si="111">SUM(U59:U62)</f>
         <v>5353</v>
       </c>
       <c r="V63" s="6">
-        <f t="shared" ref="V63" si="108">SUM(V59:V62)</f>
+        <f t="shared" ref="V63" si="112">SUM(V59:V62)</f>
         <v>5365</v>
       </c>
       <c r="W63" s="27"/>
@@ -5371,35 +5438,35 @@
         <v>55</v>
       </c>
       <c r="C64" s="24">
-        <f t="shared" ref="C64:J64" si="109">C63+C58</f>
+        <f t="shared" ref="C64:J64" si="113">C63+C58</f>
         <v>8747</v>
       </c>
       <c r="D64" s="24">
-        <f t="shared" si="109"/>
+        <f t="shared" si="113"/>
         <v>0</v>
       </c>
       <c r="E64" s="24">
-        <f t="shared" si="109"/>
+        <f t="shared" si="113"/>
         <v>0</v>
       </c>
       <c r="F64" s="24">
-        <f t="shared" si="109"/>
+        <f t="shared" si="113"/>
         <v>0</v>
       </c>
       <c r="G64" s="24">
-        <f t="shared" si="109"/>
+        <f t="shared" si="113"/>
         <v>8201</v>
       </c>
       <c r="H64" s="24">
-        <f t="shared" si="109"/>
+        <f t="shared" si="113"/>
         <v>0</v>
       </c>
       <c r="I64" s="24">
-        <f t="shared" si="109"/>
+        <f t="shared" si="113"/>
         <v>0</v>
       </c>
       <c r="J64" s="24">
-        <f t="shared" si="109"/>
+        <f t="shared" si="113"/>
         <v>0</v>
       </c>
       <c r="K64" s="24"/>
@@ -5408,31 +5475,31 @@
       <c r="N64" s="6"/>
       <c r="O64" s="6"/>
       <c r="P64" s="24">
-        <f t="shared" ref="P64:V64" si="110">P63+P58</f>
+        <f t="shared" ref="P64:V64" si="114">P63+P58</f>
         <v>0</v>
       </c>
       <c r="Q64" s="24">
-        <f t="shared" si="110"/>
+        <f t="shared" si="114"/>
         <v>0</v>
       </c>
       <c r="R64" s="24">
-        <f t="shared" si="110"/>
+        <f t="shared" si="114"/>
         <v>0</v>
       </c>
       <c r="S64" s="24">
-        <f t="shared" si="110"/>
+        <f t="shared" si="114"/>
         <v>0</v>
       </c>
       <c r="T64" s="24">
-        <f t="shared" si="110"/>
+        <f t="shared" si="114"/>
         <v>9153</v>
       </c>
       <c r="U64" s="24">
-        <f t="shared" si="110"/>
+        <f t="shared" si="114"/>
         <v>8449</v>
       </c>
       <c r="V64" s="24">
-        <f t="shared" si="110"/>
+        <f t="shared" si="114"/>
         <v>8621</v>
       </c>
       <c r="W64" s="27"/>
@@ -5640,31 +5707,31 @@
         <v>2185</v>
       </c>
       <c r="D69" s="6">
-        <f t="shared" ref="D69:J69" si="111">SUM(D65:D68)</f>
+        <f t="shared" ref="D69:J69" si="115">SUM(D65:D68)</f>
         <v>0</v>
       </c>
       <c r="E69" s="6">
-        <f t="shared" si="111"/>
+        <f t="shared" si="115"/>
         <v>0</v>
       </c>
       <c r="F69" s="6">
-        <f t="shared" si="111"/>
+        <f t="shared" si="115"/>
         <v>0</v>
       </c>
       <c r="G69" s="6">
-        <f t="shared" si="111"/>
+        <f t="shared" si="115"/>
         <v>2707</v>
       </c>
       <c r="H69" s="6">
-        <f t="shared" si="111"/>
+        <f t="shared" si="115"/>
         <v>0</v>
       </c>
       <c r="I69" s="6">
-        <f t="shared" si="111"/>
+        <f t="shared" si="115"/>
         <v>0</v>
       </c>
       <c r="J69" s="6">
-        <f t="shared" si="111"/>
+        <f t="shared" si="115"/>
         <v>0</v>
       </c>
       <c r="K69" s="6"/>
@@ -5673,31 +5740,31 @@
       <c r="N69" s="6"/>
       <c r="O69" s="6"/>
       <c r="P69" s="6">
-        <f t="shared" ref="P69" si="112">SUM(P65:P68)</f>
+        <f t="shared" ref="P69" si="116">SUM(P65:P68)</f>
         <v>0</v>
       </c>
       <c r="Q69" s="6">
-        <f t="shared" ref="Q69" si="113">SUM(Q65:Q68)</f>
+        <f t="shared" ref="Q69" si="117">SUM(Q65:Q68)</f>
         <v>0</v>
       </c>
       <c r="R69" s="6">
-        <f t="shared" ref="R69" si="114">SUM(R65:R68)</f>
+        <f t="shared" ref="R69" si="118">SUM(R65:R68)</f>
         <v>0</v>
       </c>
       <c r="S69" s="6">
-        <f t="shared" ref="S69" si="115">SUM(S65:S68)</f>
+        <f t="shared" ref="S69" si="119">SUM(S65:S68)</f>
         <v>0</v>
       </c>
       <c r="T69" s="6">
-        <f t="shared" ref="T69" si="116">SUM(T65:T68)</f>
+        <f t="shared" ref="T69" si="120">SUM(T65:T68)</f>
         <v>2233</v>
       </c>
       <c r="U69" s="6">
-        <f t="shared" ref="U69" si="117">SUM(U65:U68)</f>
+        <f t="shared" ref="U69" si="121">SUM(U65:U68)</f>
         <v>2595</v>
       </c>
       <c r="V69" s="6">
-        <f t="shared" ref="V69" si="118">SUM(V65:V68)</f>
+        <f t="shared" ref="V69" si="122">SUM(V65:V68)</f>
         <v>3264</v>
       </c>
       <c r="W69" s="27"/>
@@ -5717,35 +5784,35 @@
         <v>61</v>
       </c>
       <c r="C70" s="24">
-        <f t="shared" ref="C70:J70" si="119">C69+C64</f>
+        <f t="shared" ref="C70:J70" si="123">C69+C64</f>
         <v>10932</v>
       </c>
       <c r="D70" s="24">
-        <f t="shared" si="119"/>
+        <f t="shared" si="123"/>
         <v>0</v>
       </c>
       <c r="E70" s="24">
-        <f t="shared" si="119"/>
+        <f t="shared" si="123"/>
         <v>0</v>
       </c>
       <c r="F70" s="24">
-        <f t="shared" si="119"/>
+        <f t="shared" si="123"/>
         <v>0</v>
       </c>
       <c r="G70" s="24">
-        <f t="shared" si="119"/>
+        <f t="shared" si="123"/>
         <v>10908</v>
       </c>
       <c r="H70" s="24">
-        <f t="shared" si="119"/>
+        <f t="shared" si="123"/>
         <v>0</v>
       </c>
       <c r="I70" s="24">
-        <f t="shared" si="119"/>
+        <f t="shared" si="123"/>
         <v>0</v>
       </c>
       <c r="J70" s="24">
-        <f t="shared" si="119"/>
+        <f t="shared" si="123"/>
         <v>0</v>
       </c>
       <c r="K70" s="24"/>
@@ -5754,31 +5821,31 @@
       <c r="N70" s="6"/>
       <c r="O70" s="6"/>
       <c r="P70" s="24">
-        <f t="shared" ref="P70:V70" si="120">P69+P64</f>
+        <f t="shared" ref="P70:V70" si="124">P69+P64</f>
         <v>0</v>
       </c>
       <c r="Q70" s="24">
-        <f t="shared" si="120"/>
+        <f t="shared" si="124"/>
         <v>0</v>
       </c>
       <c r="R70" s="24">
-        <f t="shared" si="120"/>
+        <f t="shared" si="124"/>
         <v>0</v>
       </c>
       <c r="S70" s="24">
-        <f t="shared" si="120"/>
+        <f t="shared" si="124"/>
         <v>0</v>
       </c>
       <c r="T70" s="24">
-        <f t="shared" si="120"/>
+        <f t="shared" si="124"/>
         <v>11386</v>
       </c>
       <c r="U70" s="24">
-        <f t="shared" si="120"/>
+        <f t="shared" si="124"/>
         <v>11044</v>
       </c>
       <c r="V70" s="24">
-        <f t="shared" si="120"/>
+        <f t="shared" si="124"/>
         <v>11885</v>
       </c>
       <c r="W70" s="27"/>
@@ -5831,35 +5898,35 @@
         <v>30</v>
       </c>
       <c r="C72" s="6">
-        <f t="shared" ref="C72:J72" si="121">C24</f>
+        <f t="shared" ref="C72:J72" si="125">C24</f>
         <v>-18</v>
       </c>
       <c r="D72" s="6">
-        <f t="shared" si="121"/>
+        <f t="shared" si="125"/>
         <v>117</v>
       </c>
       <c r="E72" s="6">
-        <f t="shared" si="121"/>
+        <f t="shared" si="125"/>
         <v>218</v>
       </c>
       <c r="F72" s="6">
-        <f t="shared" si="121"/>
+        <f t="shared" si="125"/>
         <v>185</v>
       </c>
       <c r="G72" s="6">
-        <f t="shared" si="121"/>
+        <f t="shared" si="125"/>
         <v>158</v>
       </c>
       <c r="H72" s="6">
-        <f t="shared" si="121"/>
+        <f t="shared" si="125"/>
         <v>206</v>
       </c>
       <c r="I72" s="6">
-        <f t="shared" si="121"/>
+        <f t="shared" si="125"/>
         <v>274</v>
       </c>
       <c r="J72" s="6">
-        <f t="shared" si="121"/>
+        <f t="shared" si="125"/>
         <v>206</v>
       </c>
       <c r="K72" s="6"/>
@@ -5868,31 +5935,31 @@
       <c r="N72" s="6"/>
       <c r="O72" s="6"/>
       <c r="P72" s="6">
-        <f t="shared" ref="P72:V72" si="122">P24</f>
+        <f t="shared" ref="P72:V72" si="126">P24</f>
         <v>1003</v>
       </c>
       <c r="Q72" s="6">
-        <f t="shared" si="122"/>
+        <f t="shared" si="126"/>
         <v>351</v>
       </c>
       <c r="R72" s="6">
-        <f t="shared" si="122"/>
+        <f t="shared" si="126"/>
         <v>-665</v>
       </c>
       <c r="S72" s="6">
-        <f t="shared" si="122"/>
+        <f t="shared" si="126"/>
         <v>256</v>
       </c>
       <c r="T72" s="6">
-        <f t="shared" si="122"/>
+        <f t="shared" si="126"/>
         <v>-202</v>
       </c>
       <c r="U72" s="6">
-        <f t="shared" si="122"/>
+        <f t="shared" si="126"/>
         <v>502</v>
       </c>
       <c r="V72" s="6">
-        <f t="shared" si="122"/>
+        <f t="shared" si="126"/>
         <v>844</v>
       </c>
       <c r="W72" s="27"/>
@@ -6432,31 +6499,31 @@
         <v>-113</v>
       </c>
       <c r="D86" s="6">
-        <f t="shared" ref="D86:J86" si="123">SUM(D79:D85)</f>
+        <f t="shared" ref="D86:J86" si="127">SUM(D79:D85)</f>
         <v>0</v>
       </c>
       <c r="E86" s="6">
-        <f t="shared" si="123"/>
+        <f t="shared" si="127"/>
         <v>0</v>
       </c>
       <c r="F86" s="6">
-        <f t="shared" si="123"/>
+        <f t="shared" si="127"/>
         <v>0</v>
       </c>
       <c r="G86" s="6">
-        <f t="shared" si="123"/>
+        <f t="shared" si="127"/>
         <v>-278</v>
       </c>
       <c r="H86" s="6">
-        <f t="shared" si="123"/>
+        <f t="shared" si="127"/>
         <v>0</v>
       </c>
       <c r="I86" s="6">
-        <f t="shared" si="123"/>
+        <f t="shared" si="127"/>
         <v>0</v>
       </c>
       <c r="J86" s="6">
-        <f t="shared" si="123"/>
+        <f t="shared" si="127"/>
         <v>0</v>
       </c>
       <c r="K86" s="6"/>
@@ -6488,35 +6555,35 @@
         <v>74</v>
       </c>
       <c r="C87" s="24">
-        <f t="shared" ref="C87:J87" si="124">SUM(C72:C77)+C86</f>
+        <f t="shared" ref="C87:J87" si="128">SUM(C72:C77)+C86</f>
         <v>15</v>
       </c>
       <c r="D87" s="24">
-        <f t="shared" si="124"/>
+        <f t="shared" si="128"/>
         <v>117</v>
       </c>
       <c r="E87" s="24">
-        <f t="shared" si="124"/>
+        <f t="shared" si="128"/>
         <v>218</v>
       </c>
       <c r="F87" s="24">
-        <f t="shared" si="124"/>
+        <f t="shared" si="128"/>
         <v>185</v>
       </c>
       <c r="G87" s="24">
-        <f t="shared" si="124"/>
+        <f t="shared" si="128"/>
         <v>30</v>
       </c>
       <c r="H87" s="24">
-        <f t="shared" si="124"/>
+        <f t="shared" si="128"/>
         <v>206</v>
       </c>
       <c r="I87" s="24">
-        <f t="shared" si="124"/>
+        <f t="shared" si="128"/>
         <v>274</v>
       </c>
       <c r="J87" s="24">
-        <f t="shared" si="124"/>
+        <f t="shared" si="128"/>
         <v>206</v>
       </c>
       <c r="K87" s="24"/>
@@ -6752,31 +6819,31 @@
         <v>-30</v>
       </c>
       <c r="D93" s="24">
-        <f t="shared" ref="D93:J93" si="125">SUM(D88:D92)</f>
+        <f t="shared" ref="D93:J93" si="129">SUM(D88:D92)</f>
         <v>0</v>
       </c>
       <c r="E93" s="24">
-        <f t="shared" si="125"/>
+        <f t="shared" si="129"/>
         <v>0</v>
       </c>
       <c r="F93" s="24">
-        <f t="shared" si="125"/>
+        <f t="shared" si="129"/>
         <v>0</v>
       </c>
       <c r="G93" s="24">
-        <f t="shared" si="125"/>
+        <f t="shared" si="129"/>
         <v>-291</v>
       </c>
       <c r="H93" s="24">
-        <f t="shared" si="125"/>
+        <f t="shared" si="129"/>
         <v>0</v>
       </c>
       <c r="I93" s="24">
-        <f t="shared" si="125"/>
+        <f t="shared" si="129"/>
         <v>0</v>
       </c>
       <c r="J93" s="24">
-        <f t="shared" si="125"/>
+        <f t="shared" si="129"/>
         <v>0</v>
       </c>
       <c r="K93" s="24"/>
@@ -6932,31 +6999,31 @@
         <v>-58</v>
       </c>
       <c r="D97" s="24">
-        <f t="shared" ref="D97:J97" si="126">SUM(D94:D96)</f>
+        <f t="shared" ref="D97:J97" si="130">SUM(D94:D96)</f>
         <v>0</v>
       </c>
       <c r="E97" s="24">
-        <f t="shared" si="126"/>
+        <f t="shared" si="130"/>
         <v>0</v>
       </c>
       <c r="F97" s="24">
-        <f t="shared" si="126"/>
+        <f t="shared" si="130"/>
         <v>0</v>
       </c>
       <c r="G97" s="24">
-        <f t="shared" si="126"/>
+        <f t="shared" si="130"/>
         <v>-77</v>
       </c>
       <c r="H97" s="24">
-        <f t="shared" si="126"/>
+        <f t="shared" si="130"/>
         <v>0</v>
       </c>
       <c r="I97" s="24">
-        <f t="shared" si="126"/>
+        <f t="shared" si="130"/>
         <v>0</v>
       </c>
       <c r="J97" s="24">
-        <f t="shared" si="126"/>
+        <f t="shared" si="130"/>
         <v>0</v>
       </c>
       <c r="K97" s="24"/>
@@ -7028,19 +7095,19 @@
         <v>86</v>
       </c>
       <c r="C99" s="24">
-        <f t="shared" ref="C99:F99" si="127">C97+C93+C87+C98</f>
+        <f t="shared" ref="C99:F99" si="131">C97+C93+C87+C98</f>
         <v>-75</v>
       </c>
       <c r="D99" s="24">
-        <f t="shared" si="127"/>
+        <f t="shared" si="131"/>
         <v>117</v>
       </c>
       <c r="E99" s="24">
-        <f t="shared" si="127"/>
+        <f t="shared" si="131"/>
         <v>218</v>
       </c>
       <c r="F99" s="24">
-        <f t="shared" si="127"/>
+        <f t="shared" si="131"/>
         <v>185</v>
       </c>
       <c r="G99" s="24">
@@ -7048,15 +7115,15 @@
         <v>-340</v>
       </c>
       <c r="H99" s="24">
-        <f t="shared" ref="H99:J99" si="128">H97+H93+H87+H98</f>
+        <f t="shared" ref="H99:J99" si="132">H97+H93+H87+H98</f>
         <v>206</v>
       </c>
       <c r="I99" s="24">
-        <f t="shared" si="128"/>
+        <f t="shared" si="132"/>
         <v>274</v>
       </c>
       <c r="J99" s="24">
-        <f t="shared" si="128"/>
+        <f t="shared" si="132"/>
         <v>206</v>
       </c>
       <c r="K99" s="24"/>
